--- a/0-course-info/schedule_f26.xlsx
+++ b/0-course-info/schedule_f26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/course-info/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/czmann/Documents/teaching/stat3540/0-course-info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450A882D-1490-BA4B-963D-F3266B08D890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C726383F-547B-8444-95A1-87A884512239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" xr2:uid="{44A96070-E6A5-4735-BA92-AD6DC359C4CB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="130">
   <si>
     <t>Day</t>
   </si>
@@ -365,10 +365,6 @@
     <t>Lecture Video: Intro to Power</t>
   </si>
   <si>
-    <t>Syllabus quiz + intro survey
-Lecture Video: Controlling for Variability</t>
-  </si>
-  <si>
     <t>Activity 3.1 + Start Lab 2</t>
   </si>
   <si>
@@ -376,9 +372,6 @@
   </si>
   <si>
     <t>Activity 4.1</t>
-  </si>
-  <si>
-    <t>Lab 1 due 9/4</t>
   </si>
   <si>
     <t>Lab 2 due 9/25</t>
@@ -463,6 +456,16 @@
   </si>
   <si>
     <t>Mod 10: Writing Survey Instruments</t>
+  </si>
+  <si>
+    <t>Discord and R / Rstudio Setup
+Lecture Video: Controlling for Variability</t>
+  </si>
+  <si>
+    <t>Lab Group Contract due 8/30</t>
+  </si>
+  <si>
+    <t>Lab 1 due 9/8</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -820,21 +823,33 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -843,21 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1231,7 +1231,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="57">
+      <c r="A2" s="61">
         <v>1</v>
       </c>
       <c r="B2" s="3">
@@ -1254,7 +1254,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="57"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="3">
         <v>2</v>
       </c>
@@ -1269,24 +1269,26 @@
         <v>72</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="58"/>
+      <c r="A4" s="62"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="17"/>
       <c r="E4" s="47"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="12"/>
+      <c r="H4" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="59">
+      <c r="A5" s="65">
         <v>2</v>
       </c>
       <c r="B5" s="2">
@@ -1312,7 +1314,7 @@
       <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="57"/>
+      <c r="A6" s="61"/>
       <c r="B6" s="3">
         <f>B5+1</f>
         <v>4</v>
@@ -1335,19 +1337,17 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="58"/>
+      <c r="A7" s="62"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="17"/>
       <c r="E7" s="47"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="12" t="s">
-        <v>102</v>
-      </c>
+      <c r="H7" s="12"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="57">
+      <c r="A8" s="61">
         <v>3</v>
       </c>
       <c r="B8" s="3">
@@ -1368,11 +1368,14 @@
         <v>97</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="57"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="3">
         <f>B8+1</f>
         <v>6</v>
@@ -1388,14 +1391,14 @@
         <v>74</v>
       </c>
       <c r="F9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" t="s">
         <v>100</v>
       </c>
-      <c r="G9" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="10" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="17"/>
@@ -1405,7 +1408,7 @@
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="59">
+      <c r="A11" s="65">
         <v>4</v>
       </c>
       <c r="B11" s="2">
@@ -1423,14 +1426,14 @@
         <v>74</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="57"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="29">
         <f>B11+1</f>
         <v>8</v>
@@ -1445,14 +1448,14 @@
       <c r="E12" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="67" t="s">
-        <v>119</v>
-      </c>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
+      <c r="F12" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
     </row>
     <row r="13" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="58"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="17"/>
@@ -1462,7 +1465,7 @@
       <c r="H13" s="14"/>
     </row>
     <row r="14" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="59">
+      <c r="A14" s="65">
         <v>5</v>
       </c>
       <c r="B14" s="2">
@@ -1480,15 +1483,15 @@
         <v>74</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="57"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="3">
         <f>B14+1</f>
         <v>10</v>
@@ -1504,15 +1507,15 @@
         <v>76</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H15" s="14"/>
     </row>
     <row r="16" spans="1:8" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="58"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="17"/>
@@ -1520,11 +1523,11 @@
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="59">
+      <c r="A17" s="65">
         <v>6</v>
       </c>
       <c r="B17" s="2">
@@ -1542,14 +1545,14 @@
         <v>76</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="57"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="3">
         <f>B17+1</f>
         <v>12</v>
@@ -1565,14 +1568,14 @@
         <v>77</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="65" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="58"/>
+      <c r="A19" s="62"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="17"/>
@@ -1581,7 +1584,7 @@
       <c r="H19" s="20"/>
     </row>
     <row r="20" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="59">
+      <c r="A20" s="65">
         <v>7</v>
       </c>
       <c r="B20" s="2">
@@ -1599,15 +1602,15 @@
         <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A21" s="57"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="3">
         <f>B20+1</f>
         <v>14</v>
@@ -1623,25 +1626,25 @@
         <v>78</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="58"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="17"/>
-      <c r="F22" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
+      <c r="F22" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
     </row>
     <row r="23" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="59">
+      <c r="A23" s="65">
         <v>8</v>
       </c>
       <c r="B23" s="2">
@@ -1664,7 +1667,7 @@
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="57"/>
+      <c r="A24" s="61"/>
       <c r="B24" s="3">
         <f>B23+1</f>
         <v>16</v>
@@ -1682,18 +1685,18 @@
       <c r="H24" s="23"/>
     </row>
     <row r="25" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="58"/>
+      <c r="A25" s="62"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="17"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="59">
+      <c r="A26" s="65">
         <v>9</v>
       </c>
       <c r="B26" s="53">
@@ -1715,7 +1718,7 @@
       <c r="H26" s="56"/>
     </row>
     <row r="27" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="57"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="3">
         <f>B26+1</f>
         <v>18</v>
@@ -1731,12 +1734,12 @@
         <v>81</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="58"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="17"/>
@@ -1746,7 +1749,7 @@
       <c r="H28" s="12"/>
     </row>
     <row r="29" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="57">
+      <c r="A29" s="61">
         <v>10</v>
       </c>
       <c r="B29" s="2">
@@ -1766,7 +1769,7 @@
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="57"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="3">
         <f>B29+1</f>
         <v>20</v>
@@ -1779,11 +1782,11 @@
         <v>46324</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="58"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="17"/>
@@ -1793,7 +1796,7 @@
       <c r="H31" s="15"/>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="57">
+      <c r="A32" s="61">
         <v>11</v>
       </c>
       <c r="B32" s="2">
@@ -1808,14 +1811,14 @@
         <v>46329</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="57"/>
+      <c r="A33" s="61"/>
       <c r="B33" s="3">
         <f>B32+1</f>
         <v>22</v>
@@ -1828,11 +1831,11 @@
         <v>46331</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="58"/>
+      <c r="A34" s="62"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="17"/>
@@ -1842,7 +1845,7 @@
       <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="57">
+      <c r="A35" s="61">
         <v>12</v>
       </c>
       <c r="B35" s="2">
@@ -1857,12 +1860,12 @@
         <v>46336</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="57"/>
+      <c r="A36" s="61"/>
       <c r="B36" s="3">
         <f>B35+1</f>
         <v>24</v>
@@ -1875,11 +1878,11 @@
         <v>46338</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="58"/>
+      <c r="A37" s="62"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="17"/>
@@ -1889,7 +1892,7 @@
       <c r="H37" s="15"/>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="57">
+      <c r="A38" s="61">
         <v>13</v>
       </c>
       <c r="B38" s="2">
@@ -1904,12 +1907,12 @@
         <v>46343</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="57"/>
+      <c r="A39" s="61"/>
       <c r="B39" s="3">
         <f>B38+1</f>
         <v>26</v>
@@ -1926,7 +1929,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="58"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="17"/>
@@ -1934,11 +1937,11 @@
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
       <c r="H40" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="60"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="32"/>
       <c r="C41" s="31" t="s">
         <v>3</v>
@@ -1953,7 +1956,7 @@
       <c r="H41" s="34"/>
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="60"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="31"/>
       <c r="C42" s="31" t="s">
         <v>12</v>
@@ -1970,7 +1973,7 @@
       <c r="H42" s="36"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="61"/>
+      <c r="A43" s="64"/>
       <c r="B43" s="37"/>
       <c r="C43" s="37"/>
       <c r="D43" s="38"/>
@@ -1980,7 +1983,7 @@
       <c r="H43" s="40"/>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="57">
+      <c r="A44" s="61">
         <v>14</v>
       </c>
       <c r="B44" s="2">
@@ -2000,7 +2003,7 @@
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="57"/>
+      <c r="A45" s="61"/>
       <c r="B45" s="3">
         <f>B44+1</f>
         <v>28</v>
@@ -2017,7 +2020,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="58"/>
+      <c r="A46" s="62"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="17">
@@ -2030,7 +2033,7 @@
       <c r="H46" s="15"/>
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="57">
+      <c r="A47" s="61">
         <v>15</v>
       </c>
       <c r="B47" s="2">
@@ -2048,11 +2051,11 @@
         <v>84</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="57"/>
+      <c r="A48" s="61"/>
       <c r="B48" s="3">
         <f>B47+1</f>
         <v>30</v>
@@ -2068,11 +2071,11 @@
         <v>82</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="58"/>
+      <c r="A49" s="62"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="17">
@@ -2085,7 +2088,7 @@
       <c r="H49" s="15"/>
     </row>
     <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="57"/>
+      <c r="A50" s="61"/>
       <c r="B50" s="2"/>
       <c r="C50" s="3" t="s">
         <v>3</v>
@@ -2097,12 +2100,12 @@
       <c r="E50" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="H50" s="68" t="s">
-        <v>125</v>
+      <c r="H50" s="59" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="57"/>
+      <c r="A51" s="61"/>
       <c r="C51" s="3" t="s">
         <v>12</v>
       </c>
@@ -2113,10 +2116,10 @@
       <c r="E51" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="69"/>
+      <c r="H51" s="60"/>
     </row>
     <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="58"/>
+      <c r="A52" s="62"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="17"/>
@@ -2129,15 +2132,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
@@ -2149,6 +2143,15 @@
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A17:A19"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="78" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -2187,14 +2190,14 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="66" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="26"/>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="67" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="26"/>
@@ -2202,41 +2205,41 @@
       <c r="H5" s="26"/>
     </row>
     <row r="6" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B6" s="62"/>
+      <c r="B6" s="66"/>
       <c r="C6" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="63"/>
+      <c r="E6" s="67"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
-      <c r="H6" s="62"/>
+      <c r="H6" s="66"/>
     </row>
     <row r="7" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="62"/>
+      <c r="B7" s="66"/>
       <c r="C7" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="64"/>
+      <c r="D7" s="68"/>
       <c r="E7" s="25" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
-      <c r="H7" s="62"/>
+      <c r="H7" s="66"/>
     </row>
     <row r="8" spans="2:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="B8" s="62"/>
+      <c r="B8" s="66"/>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
-      <c r="F8" s="64" t="s">
+      <c r="F8" s="68" t="s">
         <v>21</v>
       </c>
       <c r="G8" s="26"/>
-      <c r="H8" s="62"/>
+      <c r="H8" s="66"/>
     </row>
     <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="27" t="s">
@@ -2247,9 +2250,9 @@
         <v>17</v>
       </c>
       <c r="E9" s="26"/>
-      <c r="F9" s="64"/>
+      <c r="F9" s="68"/>
       <c r="G9" s="28"/>
-      <c r="H9" s="62"/>
+      <c r="H9" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="5">
